--- a/data/trans_orig/P39B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023</t>
+          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>553259</t>
+          <t>554679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>581459</t>
+          <t>581505</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606173</t>
+          <t>606902</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>623901</t>
+          <t>625031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1168203</t>
+          <t>1167542</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1201003</t>
+          <t>1199578</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,82 +1084,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24561</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18380</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31902</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>54693</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>43298</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>69283</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24561</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18841</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>31681</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>54693</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>43679</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>67737</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18734</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26827</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36748</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1067837</t>
+          <t>1068416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1141447</t>
+          <t>1138214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>855083</t>
+          <t>854943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>882462</t>
+          <t>882083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1938771</t>
+          <t>1937682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2015602</t>
+          <t>2015768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26248</t>
+          <t>25605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71557</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>59053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107815</t>
+          <t>109849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,47 +1879,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15491</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>8733</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15145</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>633292</t>
+          <t>635263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>659021</t>
+          <t>660070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>861746</t>
+          <t>862845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>891549</t>
+          <t>893717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1507724</t>
+          <t>1504126</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1550098</t>
+          <t>1549807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>23330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32076</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,47 +2826,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>17445</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>10817</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>17445</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>11446</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>26417</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>852720</t>
+          <t>852801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>875478</t>
+          <t>876616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1006462</t>
+          <t>1005506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1033986</t>
+          <t>1032660</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1866495</t>
+          <t>1867906</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1903263</t>
+          <t>1902539</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25691</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>25147</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49218</t>
+          <t>46867</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>21899</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>76102</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46461</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>43238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83598</t>
+          <t>83456</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3148228</t>
+          <t>3149617</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3230814</t>
+          <t>3231408</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3352878</t>
+          <t>3355173</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3420231</t>
+          <t>3420313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6522834</t>
+          <t>6518804</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6623232</t>
+          <t>6621175</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>75003</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>120525</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>69773</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>110088</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>159994</t>
+          <t>160287</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>216101</t>
+          <t>218099</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32964</t>
+          <t>32094</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63600</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44592</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61243</t>
+          <t>61701</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Habitat-trans_orig.xlsx
@@ -725,22 +725,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>12560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>569061</t>
+          <t>617910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>554679</t>
+          <t>602371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>581505</t>
+          <t>629104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>616216</t>
+          <t>668462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606902</t>
+          <t>658921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>625031</t>
+          <t>676742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1185277</t>
+          <t>1286372</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1167542</t>
+          <t>1267584</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1199578</t>
+          <t>1301641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43580</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>19567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54693</t>
+          <t>57804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>46385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69283</t>
+          <t>72343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16641</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>620505</t>
+          <t>673404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>620505</t>
+          <t>673404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>620505</t>
+          <t>673404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>656146</t>
+          <t>709994</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>656146</t>
+          <t>709994</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>656146</t>
+          <t>709994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1276651</t>
+          <t>1383398</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1276651</t>
+          <t>1383398</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1276651</t>
+          <t>1383398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1412,27 +1412,27 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22192</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25085</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35489</t>
+          <t>37794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1099253</t>
+          <t>937645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1068416</t>
+          <t>916298</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1138214</t>
+          <t>957239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>870103</t>
+          <t>969655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>854943</t>
+          <t>951798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>882083</t>
+          <t>983109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1969356</t>
+          <t>1907301</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1937682</t>
+          <t>1881425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2015768</t>
+          <t>1931986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49812</t>
+          <t>60747</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>46746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70405</t>
+          <t>79578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>40434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>53598</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85786</t>
+          <t>101181</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109849</t>
+          <t>121562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1182961</t>
+          <t>1034212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1182961</t>
+          <t>1034212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1182961</t>
+          <t>1034212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932726</t>
+          <t>1042148</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932726</t>
+          <t>1042148</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932726</t>
+          <t>1042148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2115687</t>
+          <t>2076360</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2115687</t>
+          <t>2076360</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2115687</t>
+          <t>2076360</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>22473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>35375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>649247</t>
+          <t>737717</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>635263</t>
+          <t>720263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>660070</t>
+          <t>749341</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>876868</t>
+          <t>744203</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>862845</t>
+          <t>733519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>893717</t>
+          <t>755071</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1526115</t>
+          <t>1481920</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1504126</t>
+          <t>1464220</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1549807</t>
+          <t>1497285</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,67 +2463,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>19233</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>12810</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>28541</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>14668</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>8324</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>23330</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>684824</t>
+          <t>778373</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>684824</t>
+          <t>778373</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>684824</t>
+          <t>778373</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>908256</t>
+          <t>783552</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>908256</t>
+          <t>783552</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>908256</t>
+          <t>783552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1593080</t>
+          <t>1561925</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1593080</t>
+          <t>1561925</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1593080</t>
+          <t>1561925</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>30670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17816</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21427</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>866055</t>
+          <t>914475</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>852801</t>
+          <t>900062</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>876616</t>
+          <t>928345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1020054</t>
+          <t>1030162</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1005506</t>
+          <t>1015652</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1032660</t>
+          <t>1044733</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1886109</t>
+          <t>1944637</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1867906</t>
+          <t>1923748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1902539</t>
+          <t>1963853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>46759</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>61011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16636</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21066</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>900828</t>
+          <t>963916</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>900828</t>
+          <t>963916</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>900828</t>
+          <t>963916</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1073044</t>
+          <t>1095290</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1073044</t>
+          <t>1095290</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1073044</t>
+          <t>1095290</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1973872</t>
+          <t>2059206</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1973872</t>
+          <t>2059206</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1973872</t>
+          <t>2059206</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,27 +3453,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>31584</t>
+          <t>37105</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21899</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>60049</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>53884</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>82903</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3566,67 +3566,67 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>52203</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>41482</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>32187</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>56904</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>33177</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>23582</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>43238</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48644</t>
+          <t>58901</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>83456</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3183614</t>
+          <t>3207747</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3149617</t>
+          <t>3174851</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3231408</t>
+          <t>3237412</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3383242</t>
+          <t>3412483</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3355173</t>
+          <t>3385023</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3420313</t>
+          <t>3436917</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6566857</t>
+          <t>6620229</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6518804</t>
+          <t>6571021</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6621175</t>
+          <t>6656425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>121619</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>144890</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>90573</t>
+          <t>103357</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>71929</t>
+          <t>86826</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>122365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>224976</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>160287</t>
+          <t>199243</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>218099</t>
+          <t>256491</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>44012</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>63588</t>
+          <t>75820</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>78463</t>
+          <t>93588</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61701</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>99425</t>
+          <t>116593</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3389117</t>
+          <t>3449905</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3570173</t>
+          <t>3630984</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6959290</t>
+          <t>7080888</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
